--- a/artfynd/A 18306-2024 artfynd.xlsx
+++ b/artfynd/A 18306-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -801,6 +801,230 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>120302138</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79607</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Kolåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>406826</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6702173</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Sofia Damne</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Sofia Damne</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>120301256</v>
+      </c>
+      <c r="B4" t="n">
+        <v>78527</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kolåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>406846</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6702251</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jon Eklund</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jon Eklund</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18306-2024 artfynd.xlsx
+++ b/artfynd/A 18306-2024 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>120302138</v>
       </c>
       <c r="B3" t="n">
-        <v>79607</v>
+        <v>79623</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>120301256</v>
       </c>
       <c r="B4" t="n">
-        <v>78527</v>
+        <v>78543</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 18306-2024 artfynd.xlsx
+++ b/artfynd/A 18306-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1026,6 +1026,118 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>120301164</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kolåsen, Kolåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>406890</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6702300</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 18306-2024 artfynd.xlsx
+++ b/artfynd/A 18306-2024 artfynd.xlsx
@@ -804,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120302138</v>
+        <v>120301256</v>
       </c>
       <c r="B3" t="n">
-        <v>79623</v>
+        <v>78543</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -820,21 +820,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>230405</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -844,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>406826</v>
+        <v>406846</v>
       </c>
       <c r="R3" t="n">
-        <v>6702173</v>
+        <v>6702251</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,7 +879,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,22 +904,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sofia Damne</t>
+          <t>Jon Eklund</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sofia Damne</t>
+          <t>Jon Eklund</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120301256</v>
+        <v>120302138</v>
       </c>
       <c r="B4" t="n">
-        <v>78543</v>
+        <v>79623</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,21 +932,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>230405</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -956,10 +956,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>406846</v>
+        <v>406826</v>
       </c>
       <c r="R4" t="n">
-        <v>6702251</v>
+        <v>6702173</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -991,7 +991,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,12 +1016,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jon Eklund</t>
+          <t>Sofia Damne</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jon Eklund</t>
+          <t>Sofia Damne</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 18306-2024 artfynd.xlsx
+++ b/artfynd/A 18306-2024 artfynd.xlsx
@@ -804,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120301256</v>
+        <v>120302138</v>
       </c>
       <c r="B3" t="n">
-        <v>78543</v>
+        <v>79623</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -820,21 +820,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>230405</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -844,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>406846</v>
+        <v>406826</v>
       </c>
       <c r="R3" t="n">
-        <v>6702251</v>
+        <v>6702173</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,7 +879,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,22 +904,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jon Eklund</t>
+          <t>Sofia Damne</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jon Eklund</t>
+          <t>Sofia Damne</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120302138</v>
+        <v>120301256</v>
       </c>
       <c r="B4" t="n">
-        <v>79623</v>
+        <v>78543</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,21 +932,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>230405</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -956,10 +956,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>406826</v>
+        <v>406846</v>
       </c>
       <c r="R4" t="n">
-        <v>6702173</v>
+        <v>6702251</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -991,7 +991,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,12 +1016,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sofia Damne</t>
+          <t>Jon Eklund</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sofia Damne</t>
+          <t>Jon Eklund</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 18306-2024 artfynd.xlsx
+++ b/artfynd/A 18306-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1138,6 +1138,1963 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129645558</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80149</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Nedre värnäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>407013</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6702313</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129641280</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kolåsen, Kolåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>406953</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6702246</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jon Eklund</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jon Eklund</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129643907</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80149</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kolåsen, Kolåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>406813</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6702148</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jon Eklund</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jon Eklund</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129651079</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91606</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kolåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>407038</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6702362</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Ossian Tulin</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Ossian Tulin</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129645549</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91517</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Nedre värnäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>407002</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6702306</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129642118</v>
+      </c>
+      <c r="B11" t="n">
+        <v>96973</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>53</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kolåsen, Kolåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>406976</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6702335</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jon Eklund</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jon Eklund</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129643862</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80178</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kolåsen, Kolåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>406831</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6702177</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jon Eklund</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Jon Eklund</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129642502</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kolåsen, Kolåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>406915</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6702269</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jon Eklund</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jon Eklund</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129645561</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80109</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Nedre värnäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>407008</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6702375</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129641422</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80149</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kolåsen, Kolåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>407070</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6702351</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jon Eklund</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jon Eklund</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129651077</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80178</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Kolåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>407042</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6702373</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Ossian Tulin</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Ossian Tulin</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129651080</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80149</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Kolåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>407023</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6702296</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Ossian Tulin</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Ossian Tulin</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129650141</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Torsby kommun, Vrm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>406977</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6702311</v>
+      </c>
+      <c r="S18" t="n">
+        <v>20</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129645546</v>
+      </c>
+      <c r="B19" t="n">
+        <v>96973</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>53</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Nedre värnäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>407002</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6702306</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Moa Björnberg dillner</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129643884</v>
+      </c>
+      <c r="B20" t="n">
+        <v>80149</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Kolåsen, Kolåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>406822</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6702171</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Jon Eklund</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Jon Eklund</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129641649</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Kolåsen, Kolåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>407112</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6702395</v>
+      </c>
+      <c r="S21" t="n">
+        <v>8</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Jon Eklund</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Jon Eklund</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129643090</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80149</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Kolåsen, Kolåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>406830</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6702175</v>
+      </c>
+      <c r="S22" t="n">
+        <v>7</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Jon Eklund</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Jon Eklund</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129641549</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Kolåsen, Kolåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>407133</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6702349</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Jon Eklund</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Jon Eklund</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129642193</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79045</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Kolåsen, Kolåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>406961</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6702296</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Jon Eklund</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Jon Eklund</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 18306-2024 artfynd.xlsx
+++ b/artfynd/A 18306-2024 artfynd.xlsx
@@ -1966,48 +1966,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129645561</v>
+        <v>129641422</v>
       </c>
       <c r="B14" t="n">
-        <v>80109</v>
+        <v>80149</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Nedre värnäs, Vrm</t>
+          <t>Kolåsen, Kolåsen, Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>407008</v>
+        <v>407070</v>
       </c>
       <c r="R14" t="n">
-        <v>6702375</v>
+        <v>6702351</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2034,9 +2034,19 @@
           <t>2025-11-10</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2051,60 +2061,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Jon Eklund</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Jon Eklund</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129641422</v>
+        <v>129645561</v>
       </c>
       <c r="B15" t="n">
-        <v>80149</v>
+        <v>80109</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kolåsen, Kolåsen, Vrm</t>
+          <t>Nedre värnäs, Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>407070</v>
+        <v>407008</v>
       </c>
       <c r="R15" t="n">
-        <v>6702351</v>
+        <v>6702375</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2131,19 +2141,9 @@
           <t>2025-11-10</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>13:54</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2158,12 +2158,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Jon Eklund</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jon Eklund</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 18306-2024 artfynd.xlsx
+++ b/artfynd/A 18306-2024 artfynd.xlsx
@@ -1966,48 +1966,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129641422</v>
+        <v>129645561</v>
       </c>
       <c r="B14" t="n">
-        <v>80149</v>
+        <v>80109</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kolåsen, Kolåsen, Vrm</t>
+          <t>Nedre värnäs, Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>407070</v>
+        <v>407008</v>
       </c>
       <c r="R14" t="n">
-        <v>6702351</v>
+        <v>6702375</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2034,19 +2034,9 @@
           <t>2025-11-10</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>13:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2061,60 +2051,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Jon Eklund</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jon Eklund</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129645561</v>
+        <v>129641422</v>
       </c>
       <c r="B15" t="n">
-        <v>80109</v>
+        <v>80149</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Nedre värnäs, Vrm</t>
+          <t>Kolåsen, Kolåsen, Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>407008</v>
+        <v>407070</v>
       </c>
       <c r="R15" t="n">
-        <v>6702375</v>
+        <v>6702351</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2141,9 +2131,19 @@
           <t>2025-11-10</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2158,12 +2158,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Jon Eklund</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Jon Eklund</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2558,10 +2558,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129643884</v>
+        <v>129641649</v>
       </c>
       <c r="B20" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2569,21 +2569,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2593,13 +2593,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>406822</v>
+        <v>407112</v>
       </c>
       <c r="R20" t="n">
-        <v>6702171</v>
+        <v>6702395</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2665,10 +2665,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129641649</v>
+        <v>129643884</v>
       </c>
       <c r="B21" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2676,21 +2676,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2700,13 +2700,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>407112</v>
+        <v>406822</v>
       </c>
       <c r="R21" t="n">
-        <v>6702395</v>
+        <v>6702171</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 18306-2024 artfynd.xlsx
+++ b/artfynd/A 18306-2024 artfynd.xlsx
@@ -1143,7 +1143,7 @@
         <v>129645558</v>
       </c>
       <c r="B6" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>129641280</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>129643907</v>
       </c>
       <c r="B8" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>129651079</v>
       </c>
       <c r="B9" t="n">
-        <v>91606</v>
+        <v>91634</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>129645549</v>
       </c>
       <c r="B10" t="n">
-        <v>91517</v>
+        <v>91545</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>129642118</v>
       </c>
       <c r="B11" t="n">
-        <v>96973</v>
+        <v>97002</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>129643862</v>
       </c>
       <c r="B12" t="n">
-        <v>80178</v>
+        <v>80204</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>129642502</v>
       </c>
       <c r="B13" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1966,48 +1966,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129645561</v>
+        <v>129641422</v>
       </c>
       <c r="B14" t="n">
-        <v>80109</v>
+        <v>80175</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Nedre värnäs, Vrm</t>
+          <t>Kolåsen, Kolåsen, Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>407008</v>
+        <v>407070</v>
       </c>
       <c r="R14" t="n">
-        <v>6702375</v>
+        <v>6702351</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2034,9 +2034,19 @@
           <t>2025-11-10</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2051,60 +2061,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Jon Eklund</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Jon Eklund</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129641422</v>
+        <v>129645561</v>
       </c>
       <c r="B15" t="n">
-        <v>80149</v>
+        <v>80135</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kolåsen, Kolåsen, Vrm</t>
+          <t>Nedre värnäs, Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>407070</v>
+        <v>407008</v>
       </c>
       <c r="R15" t="n">
-        <v>6702351</v>
+        <v>6702375</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2131,19 +2141,9 @@
           <t>2025-11-10</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>13:54</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2158,12 +2158,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Jon Eklund</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jon Eklund</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2173,7 +2173,7 @@
         <v>129651077</v>
       </c>
       <c r="B16" t="n">
-        <v>80178</v>
+        <v>80204</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>129651080</v>
       </c>
       <c r="B17" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>129650141</v>
       </c>
       <c r="B18" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>129645546</v>
       </c>
       <c r="B19" t="n">
-        <v>96973</v>
+        <v>97002</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2558,10 +2558,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129641649</v>
+        <v>129643884</v>
       </c>
       <c r="B20" t="n">
-        <v>79044</v>
+        <v>80175</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2569,21 +2569,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2593,13 +2593,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>407112</v>
+        <v>406822</v>
       </c>
       <c r="R20" t="n">
-        <v>6702395</v>
+        <v>6702171</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2665,10 +2665,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129643884</v>
+        <v>129641649</v>
       </c>
       <c r="B21" t="n">
-        <v>80149</v>
+        <v>79070</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2676,21 +2676,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2700,13 +2700,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>406822</v>
+        <v>407112</v>
       </c>
       <c r="R21" t="n">
-        <v>6702171</v>
+        <v>6702395</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2775,7 +2775,7 @@
         <v>129643090</v>
       </c>
       <c r="B22" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>129641549</v>
       </c>
       <c r="B23" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>129642193</v>
       </c>
       <c r="B24" t="n">
-        <v>79045</v>
+        <v>79071</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 18306-2024 artfynd.xlsx
+++ b/artfynd/A 18306-2024 artfynd.xlsx
@@ -1143,7 +1143,7 @@
         <v>129645558</v>
       </c>
       <c r="B6" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>129641280</v>
       </c>
       <c r="B7" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>129643907</v>
       </c>
       <c r="B8" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>129651079</v>
       </c>
       <c r="B9" t="n">
-        <v>91634</v>
+        <v>91640</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>129645549</v>
       </c>
       <c r="B10" t="n">
-        <v>91545</v>
+        <v>91551</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>129642118</v>
       </c>
       <c r="B11" t="n">
-        <v>97002</v>
+        <v>97014</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>129643862</v>
       </c>
       <c r="B12" t="n">
-        <v>80204</v>
+        <v>80209</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>129642502</v>
       </c>
       <c r="B13" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>129641422</v>
       </c>
       <c r="B14" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>129645561</v>
       </c>
       <c r="B15" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2170,32 +2170,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129651077</v>
+        <v>129651080</v>
       </c>
       <c r="B16" t="n">
-        <v>80204</v>
+        <v>80180</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2205,10 +2205,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>407042</v>
+        <v>407023</v>
       </c>
       <c r="R16" t="n">
-        <v>6702373</v>
+        <v>6702296</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2267,32 +2267,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129651080</v>
+        <v>129651077</v>
       </c>
       <c r="B17" t="n">
-        <v>80175</v>
+        <v>80209</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2302,10 +2302,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>407023</v>
+        <v>407042</v>
       </c>
       <c r="R17" t="n">
-        <v>6702296</v>
+        <v>6702373</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2367,7 +2367,7 @@
         <v>129650141</v>
       </c>
       <c r="B18" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>129645546</v>
       </c>
       <c r="B19" t="n">
-        <v>97002</v>
+        <v>97014</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         <v>129643884</v>
       </c>
       <c r="B20" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>129641649</v>
       </c>
       <c r="B21" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>129643090</v>
       </c>
       <c r="B22" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>129641549</v>
       </c>
       <c r="B23" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>129642193</v>
       </c>
       <c r="B24" t="n">
-        <v>79071</v>
+        <v>79076</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 18306-2024 artfynd.xlsx
+++ b/artfynd/A 18306-2024 artfynd.xlsx
@@ -1143,7 +1143,7 @@
         <v>129645558</v>
       </c>
       <c r="B6" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>129641280</v>
       </c>
       <c r="B7" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>129643907</v>
       </c>
       <c r="B8" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>129651079</v>
       </c>
       <c r="B9" t="n">
-        <v>91640</v>
+        <v>91641</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>129645549</v>
       </c>
       <c r="B10" t="n">
-        <v>91551</v>
+        <v>91552</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>129642118</v>
       </c>
       <c r="B11" t="n">
-        <v>97014</v>
+        <v>97015</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>129643862</v>
       </c>
       <c r="B12" t="n">
-        <v>80209</v>
+        <v>80210</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>129642502</v>
       </c>
       <c r="B13" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>129641422</v>
       </c>
       <c r="B14" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>129645561</v>
       </c>
       <c r="B15" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2170,32 +2170,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129651080</v>
+        <v>129651077</v>
       </c>
       <c r="B16" t="n">
-        <v>80180</v>
+        <v>80210</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2205,10 +2205,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>407023</v>
+        <v>407042</v>
       </c>
       <c r="R16" t="n">
-        <v>6702296</v>
+        <v>6702373</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2267,32 +2267,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129651077</v>
+        <v>129651080</v>
       </c>
       <c r="B17" t="n">
-        <v>80209</v>
+        <v>80181</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2302,10 +2302,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>407042</v>
+        <v>407023</v>
       </c>
       <c r="R17" t="n">
-        <v>6702373</v>
+        <v>6702296</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2367,7 +2367,7 @@
         <v>129650141</v>
       </c>
       <c r="B18" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>129645546</v>
       </c>
       <c r="B19" t="n">
-        <v>97014</v>
+        <v>97015</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2558,10 +2558,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129643884</v>
+        <v>129641649</v>
       </c>
       <c r="B20" t="n">
-        <v>80180</v>
+        <v>79076</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2569,21 +2569,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2593,13 +2593,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>406822</v>
+        <v>407112</v>
       </c>
       <c r="R20" t="n">
-        <v>6702171</v>
+        <v>6702395</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2665,10 +2665,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129641649</v>
+        <v>129643884</v>
       </c>
       <c r="B21" t="n">
-        <v>79075</v>
+        <v>80181</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2676,21 +2676,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2700,13 +2700,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>407112</v>
+        <v>406822</v>
       </c>
       <c r="R21" t="n">
-        <v>6702395</v>
+        <v>6702171</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2775,7 +2775,7 @@
         <v>129643090</v>
       </c>
       <c r="B22" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>129641549</v>
       </c>
       <c r="B23" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>129642193</v>
       </c>
       <c r="B24" t="n">
-        <v>79076</v>
+        <v>79077</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 18306-2024 artfynd.xlsx
+++ b/artfynd/A 18306-2024 artfynd.xlsx
@@ -1140,10 +1140,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129645558</v>
+        <v>129641280</v>
       </c>
       <c r="B6" t="n">
-        <v>80181</v>
+        <v>79076</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1151,37 +1151,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nedre värnäs, Vrm</t>
+          <t>Kolåsen, Kolåsen, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>407013</v>
+        <v>406953</v>
       </c>
       <c r="R6" t="n">
-        <v>6702313</v>
+        <v>6702246</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1208,9 +1208,19 @@
           <t>2025-11-10</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,22 +1235,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Jon Eklund</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Jon Eklund</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129641280</v>
+        <v>129645558</v>
       </c>
       <c r="B7" t="n">
-        <v>79076</v>
+        <v>80181</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1248,37 +1258,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kolåsen, Kolåsen, Vrm</t>
+          <t>Nedre värnäs, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>406953</v>
+        <v>407013</v>
       </c>
       <c r="R7" t="n">
-        <v>6702246</v>
+        <v>6702313</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1305,19 +1315,9 @@
           <t>2025-11-10</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>13:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,12 +1332,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jon Eklund</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jon Eklund</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 18306-2024 artfynd.xlsx
+++ b/artfynd/A 18306-2024 artfynd.xlsx
@@ -1143,7 +1143,7 @@
         <v>129641280</v>
       </c>
       <c r="B6" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>129645558</v>
       </c>
       <c r="B7" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>129643907</v>
       </c>
       <c r="B8" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>129651079</v>
       </c>
       <c r="B9" t="n">
-        <v>91641</v>
+        <v>91646</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>129645549</v>
       </c>
       <c r="B10" t="n">
-        <v>91552</v>
+        <v>91557</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>129642118</v>
       </c>
       <c r="B11" t="n">
-        <v>97015</v>
+        <v>97020</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>129643862</v>
       </c>
       <c r="B12" t="n">
-        <v>80210</v>
+        <v>80215</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>129642502</v>
       </c>
       <c r="B13" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1966,48 +1966,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129641422</v>
+        <v>129645561</v>
       </c>
       <c r="B14" t="n">
-        <v>80181</v>
+        <v>80146</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kolåsen, Kolåsen, Vrm</t>
+          <t>Nedre värnäs, Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>407070</v>
+        <v>407008</v>
       </c>
       <c r="R14" t="n">
-        <v>6702351</v>
+        <v>6702375</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2034,19 +2034,9 @@
           <t>2025-11-10</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>13:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2061,60 +2051,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Jon Eklund</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jon Eklund</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129645561</v>
+        <v>129641422</v>
       </c>
       <c r="B15" t="n">
-        <v>80141</v>
+        <v>80186</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Nedre värnäs, Vrm</t>
+          <t>Kolåsen, Kolåsen, Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>407008</v>
+        <v>407070</v>
       </c>
       <c r="R15" t="n">
-        <v>6702375</v>
+        <v>6702351</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2141,9 +2131,19 @@
           <t>2025-11-10</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2158,12 +2158,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Jon Eklund</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Jon Eklund</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2173,7 +2173,7 @@
         <v>129651077</v>
       </c>
       <c r="B16" t="n">
-        <v>80210</v>
+        <v>80215</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>129651080</v>
       </c>
       <c r="B17" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>129650141</v>
       </c>
       <c r="B18" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>129645546</v>
       </c>
       <c r="B19" t="n">
-        <v>97015</v>
+        <v>97020</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         <v>129641649</v>
       </c>
       <c r="B20" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>129643884</v>
       </c>
       <c r="B21" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>129643090</v>
       </c>
       <c r="B22" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>129641549</v>
       </c>
       <c r="B23" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>129642193</v>
       </c>
       <c r="B24" t="n">
-        <v>79077</v>
+        <v>79082</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 18306-2024 artfynd.xlsx
+++ b/artfynd/A 18306-2024 artfynd.xlsx
@@ -1140,10 +1140,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129641280</v>
+        <v>129645558</v>
       </c>
       <c r="B6" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1151,37 +1151,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kolåsen, Kolåsen, Vrm</t>
+          <t>Nedre värnäs, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>406953</v>
+        <v>407013</v>
       </c>
       <c r="R6" t="n">
-        <v>6702246</v>
+        <v>6702313</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1208,19 +1208,9 @@
           <t>2025-11-10</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:39</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,22 +1225,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jon Eklund</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jon Eklund</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129645558</v>
+        <v>129641280</v>
       </c>
       <c r="B7" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1258,37 +1248,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nedre värnäs, Vrm</t>
+          <t>Kolåsen, Kolåsen, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>407013</v>
+        <v>406953</v>
       </c>
       <c r="R7" t="n">
-        <v>6702313</v>
+        <v>6702246</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1315,9 +1305,19 @@
           <t>2025-11-10</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,12 +1332,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Jon Eklund</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Jon Eklund</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1966,48 +1966,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129645561</v>
+        <v>129641422</v>
       </c>
       <c r="B14" t="n">
-        <v>80146</v>
+        <v>80186</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Nedre värnäs, Vrm</t>
+          <t>Kolåsen, Kolåsen, Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>407008</v>
+        <v>407070</v>
       </c>
       <c r="R14" t="n">
-        <v>6702375</v>
+        <v>6702351</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2034,9 +2034,19 @@
           <t>2025-11-10</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2051,60 +2061,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Jon Eklund</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Jon Eklund</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129641422</v>
+        <v>129645561</v>
       </c>
       <c r="B15" t="n">
-        <v>80186</v>
+        <v>80146</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kolåsen, Kolåsen, Vrm</t>
+          <t>Nedre värnäs, Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>407070</v>
+        <v>407008</v>
       </c>
       <c r="R15" t="n">
-        <v>6702351</v>
+        <v>6702375</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2131,19 +2141,9 @@
           <t>2025-11-10</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>13:54</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2158,12 +2158,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Jon Eklund</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jon Eklund</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 18306-2024 artfynd.xlsx
+++ b/artfynd/A 18306-2024 artfynd.xlsx
@@ -1140,10 +1140,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129645558</v>
+        <v>129641280</v>
       </c>
       <c r="B6" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1151,37 +1151,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nedre värnäs, Vrm</t>
+          <t>Kolåsen, Kolåsen, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>407013</v>
+        <v>406953</v>
       </c>
       <c r="R6" t="n">
-        <v>6702313</v>
+        <v>6702246</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1208,9 +1208,19 @@
           <t>2025-11-10</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,22 +1235,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Jon Eklund</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Jon Eklund</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129641280</v>
+        <v>129645558</v>
       </c>
       <c r="B7" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1248,37 +1258,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kolåsen, Kolåsen, Vrm</t>
+          <t>Nedre värnäs, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>406953</v>
+        <v>407013</v>
       </c>
       <c r="R7" t="n">
-        <v>6702246</v>
+        <v>6702313</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1305,19 +1315,9 @@
           <t>2025-11-10</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>13:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,12 +1332,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jon Eklund</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jon Eklund</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -2558,10 +2558,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129641649</v>
+        <v>129643884</v>
       </c>
       <c r="B20" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2569,21 +2569,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2593,13 +2593,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>407112</v>
+        <v>406822</v>
       </c>
       <c r="R20" t="n">
-        <v>6702395</v>
+        <v>6702171</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2665,10 +2665,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129643884</v>
+        <v>129641649</v>
       </c>
       <c r="B21" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2676,21 +2676,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2700,13 +2700,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>406822</v>
+        <v>407112</v>
       </c>
       <c r="R21" t="n">
-        <v>6702171</v>
+        <v>6702395</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 18306-2024 artfynd.xlsx
+++ b/artfynd/A 18306-2024 artfynd.xlsx
@@ -2558,10 +2558,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129643884</v>
+        <v>129641649</v>
       </c>
       <c r="B20" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2569,21 +2569,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2593,13 +2593,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>406822</v>
+        <v>407112</v>
       </c>
       <c r="R20" t="n">
-        <v>6702171</v>
+        <v>6702395</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2665,10 +2665,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129641649</v>
+        <v>129643884</v>
       </c>
       <c r="B21" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2676,21 +2676,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2700,13 +2700,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>407112</v>
+        <v>406822</v>
       </c>
       <c r="R21" t="n">
-        <v>6702395</v>
+        <v>6702171</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 18306-2024 artfynd.xlsx
+++ b/artfynd/A 18306-2024 artfynd.xlsx
@@ -1140,10 +1140,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129641280</v>
+        <v>129645558</v>
       </c>
       <c r="B6" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1151,37 +1151,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kolåsen, Kolåsen, Vrm</t>
+          <t>Nedre värnäs, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>406953</v>
+        <v>407013</v>
       </c>
       <c r="R6" t="n">
-        <v>6702246</v>
+        <v>6702313</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1208,19 +1208,9 @@
           <t>2025-11-10</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:39</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,22 +1225,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jon Eklund</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jon Eklund</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129645558</v>
+        <v>129641280</v>
       </c>
       <c r="B7" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1258,37 +1248,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nedre värnäs, Vrm</t>
+          <t>Kolåsen, Kolåsen, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>407013</v>
+        <v>406953</v>
       </c>
       <c r="R7" t="n">
-        <v>6702313</v>
+        <v>6702246</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1315,9 +1305,19 @@
           <t>2025-11-10</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,12 +1332,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Jon Eklund</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Jon Eklund</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1454,7 +1454,7 @@
         <v>129651079</v>
       </c>
       <c r="B9" t="n">
-        <v>91646</v>
+        <v>91650</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>129645549</v>
       </c>
       <c r="B10" t="n">
-        <v>91557</v>
+        <v>91561</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>129642118</v>
       </c>
       <c r="B11" t="n">
-        <v>97020</v>
+        <v>97024</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1966,48 +1966,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129641422</v>
+        <v>129645561</v>
       </c>
       <c r="B14" t="n">
-        <v>80186</v>
+        <v>80146</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kolåsen, Kolåsen, Vrm</t>
+          <t>Nedre värnäs, Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>407070</v>
+        <v>407008</v>
       </c>
       <c r="R14" t="n">
-        <v>6702351</v>
+        <v>6702375</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2034,19 +2034,9 @@
           <t>2025-11-10</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>13:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2061,60 +2051,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Jon Eklund</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jon Eklund</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129645561</v>
+        <v>129641422</v>
       </c>
       <c r="B15" t="n">
-        <v>80146</v>
+        <v>80186</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Nedre värnäs, Vrm</t>
+          <t>Kolåsen, Kolåsen, Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>407008</v>
+        <v>407070</v>
       </c>
       <c r="R15" t="n">
-        <v>6702375</v>
+        <v>6702351</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2141,9 +2131,19 @@
           <t>2025-11-10</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2158,44 +2158,44 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Jon Eklund</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Jon Eklund</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129651077</v>
+        <v>129651080</v>
       </c>
       <c r="B16" t="n">
-        <v>80215</v>
+        <v>80186</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2205,10 +2205,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>407042</v>
+        <v>407023</v>
       </c>
       <c r="R16" t="n">
-        <v>6702373</v>
+        <v>6702296</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2267,32 +2267,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129651080</v>
+        <v>129651077</v>
       </c>
       <c r="B17" t="n">
-        <v>80186</v>
+        <v>80215</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2302,10 +2302,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>407023</v>
+        <v>407042</v>
       </c>
       <c r="R17" t="n">
-        <v>6702296</v>
+        <v>6702373</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2464,7 +2464,7 @@
         <v>129645546</v>
       </c>
       <c r="B19" t="n">
-        <v>97020</v>
+        <v>97024</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2558,10 +2558,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129641649</v>
+        <v>129643884</v>
       </c>
       <c r="B20" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2569,21 +2569,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2593,13 +2593,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>407112</v>
+        <v>406822</v>
       </c>
       <c r="R20" t="n">
-        <v>6702395</v>
+        <v>6702171</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2665,10 +2665,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129643884</v>
+        <v>129641649</v>
       </c>
       <c r="B21" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2676,21 +2676,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2700,13 +2700,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>406822</v>
+        <v>407112</v>
       </c>
       <c r="R21" t="n">
-        <v>6702171</v>
+        <v>6702395</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 18306-2024 artfynd.xlsx
+++ b/artfynd/A 18306-2024 artfynd.xlsx
@@ -1140,10 +1140,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129645558</v>
+        <v>129641280</v>
       </c>
       <c r="B6" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1151,37 +1151,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nedre värnäs, Vrm</t>
+          <t>Kolåsen, Kolåsen, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>407013</v>
+        <v>406953</v>
       </c>
       <c r="R6" t="n">
-        <v>6702313</v>
+        <v>6702246</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1208,9 +1208,19 @@
           <t>2025-11-10</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,22 +1235,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Jon Eklund</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Jon Eklund</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129641280</v>
+        <v>129645558</v>
       </c>
       <c r="B7" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1248,37 +1258,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kolåsen, Kolåsen, Vrm</t>
+          <t>Nedre värnäs, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>406953</v>
+        <v>407013</v>
       </c>
       <c r="R7" t="n">
-        <v>6702246</v>
+        <v>6702313</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1305,19 +1315,9 @@
           <t>2025-11-10</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>13:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,12 +1332,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jon Eklund</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jon Eklund</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1454,7 +1454,7 @@
         <v>129651079</v>
       </c>
       <c r="B9" t="n">
-        <v>91650</v>
+        <v>91652</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>129645549</v>
       </c>
       <c r="B10" t="n">
-        <v>91561</v>
+        <v>91563</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>129642118</v>
       </c>
       <c r="B11" t="n">
-        <v>97024</v>
+        <v>97026</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1966,48 +1966,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129645561</v>
+        <v>129641422</v>
       </c>
       <c r="B14" t="n">
-        <v>80146</v>
+        <v>80186</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Nedre värnäs, Vrm</t>
+          <t>Kolåsen, Kolåsen, Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>407008</v>
+        <v>407070</v>
       </c>
       <c r="R14" t="n">
-        <v>6702375</v>
+        <v>6702351</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2034,9 +2034,19 @@
           <t>2025-11-10</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2051,60 +2061,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Jon Eklund</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Jon Eklund</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129641422</v>
+        <v>129645561</v>
       </c>
       <c r="B15" t="n">
-        <v>80186</v>
+        <v>80146</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kolåsen, Kolåsen, Vrm</t>
+          <t>Nedre värnäs, Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>407070</v>
+        <v>407008</v>
       </c>
       <c r="R15" t="n">
-        <v>6702351</v>
+        <v>6702375</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2131,19 +2141,9 @@
           <t>2025-11-10</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>13:54</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2158,44 +2158,44 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Jon Eklund</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jon Eklund</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129651080</v>
+        <v>129651077</v>
       </c>
       <c r="B16" t="n">
-        <v>80186</v>
+        <v>80215</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2205,10 +2205,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>407023</v>
+        <v>407042</v>
       </c>
       <c r="R16" t="n">
-        <v>6702296</v>
+        <v>6702373</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2267,32 +2267,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129651077</v>
+        <v>129651080</v>
       </c>
       <c r="B17" t="n">
-        <v>80215</v>
+        <v>80186</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2302,10 +2302,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>407042</v>
+        <v>407023</v>
       </c>
       <c r="R17" t="n">
-        <v>6702373</v>
+        <v>6702296</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2464,7 +2464,7 @@
         <v>129645546</v>
       </c>
       <c r="B19" t="n">
-        <v>97024</v>
+        <v>97026</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2558,10 +2558,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129643884</v>
+        <v>129641649</v>
       </c>
       <c r="B20" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2569,21 +2569,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2593,13 +2593,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>406822</v>
+        <v>407112</v>
       </c>
       <c r="R20" t="n">
-        <v>6702171</v>
+        <v>6702395</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2665,10 +2665,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129641649</v>
+        <v>129643884</v>
       </c>
       <c r="B21" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2676,21 +2676,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2700,13 +2700,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>407112</v>
+        <v>406822</v>
       </c>
       <c r="R21" t="n">
-        <v>6702395</v>
+        <v>6702171</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 18306-2024 artfynd.xlsx
+++ b/artfynd/A 18306-2024 artfynd.xlsx
@@ -1140,10 +1140,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129641280</v>
+        <v>129645558</v>
       </c>
       <c r="B6" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1151,37 +1151,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kolåsen, Kolåsen, Vrm</t>
+          <t>Nedre värnäs, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>406953</v>
+        <v>407013</v>
       </c>
       <c r="R6" t="n">
-        <v>6702246</v>
+        <v>6702313</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1208,19 +1208,9 @@
           <t>2025-11-10</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:39</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,22 +1225,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jon Eklund</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jon Eklund</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129645558</v>
+        <v>129641280</v>
       </c>
       <c r="B7" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1258,37 +1248,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nedre värnäs, Vrm</t>
+          <t>Kolåsen, Kolåsen, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>407013</v>
+        <v>406953</v>
       </c>
       <c r="R7" t="n">
-        <v>6702313</v>
+        <v>6702246</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1315,9 +1305,19 @@
           <t>2025-11-10</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,12 +1332,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Jon Eklund</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Jon Eklund</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1648,7 +1648,7 @@
         <v>129642118</v>
       </c>
       <c r="B11" t="n">
-        <v>97026</v>
+        <v>97036</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>129645546</v>
       </c>
       <c r="B19" t="n">
-        <v>97026</v>
+        <v>97036</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 18306-2024 artfynd.xlsx
+++ b/artfynd/A 18306-2024 artfynd.xlsx
@@ -2558,10 +2558,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129641649</v>
+        <v>129643884</v>
       </c>
       <c r="B20" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2569,21 +2569,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2593,13 +2593,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>407112</v>
+        <v>406822</v>
       </c>
       <c r="R20" t="n">
-        <v>6702395</v>
+        <v>6702171</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2665,10 +2665,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129643884</v>
+        <v>129641649</v>
       </c>
       <c r="B21" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2676,21 +2676,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2700,13 +2700,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>406822</v>
+        <v>407112</v>
       </c>
       <c r="R21" t="n">
-        <v>6702171</v>
+        <v>6702395</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 18306-2024 artfynd.xlsx
+++ b/artfynd/A 18306-2024 artfynd.xlsx
@@ -1966,48 +1966,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129641422</v>
+        <v>129645561</v>
       </c>
       <c r="B14" t="n">
-        <v>80186</v>
+        <v>80146</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kolåsen, Kolåsen, Vrm</t>
+          <t>Nedre värnäs, Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>407070</v>
+        <v>407008</v>
       </c>
       <c r="R14" t="n">
-        <v>6702351</v>
+        <v>6702375</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2034,19 +2034,9 @@
           <t>2025-11-10</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>13:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2061,60 +2051,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Jon Eklund</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jon Eklund</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129645561</v>
+        <v>129641422</v>
       </c>
       <c r="B15" t="n">
-        <v>80146</v>
+        <v>80186</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Nedre värnäs, Vrm</t>
+          <t>Kolåsen, Kolåsen, Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>407008</v>
+        <v>407070</v>
       </c>
       <c r="R15" t="n">
-        <v>6702375</v>
+        <v>6702351</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2141,9 +2131,19 @@
           <t>2025-11-10</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2158,12 +2158,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Jon Eklund</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Jon Eklund</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2558,10 +2558,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129643884</v>
+        <v>129641649</v>
       </c>
       <c r="B20" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2569,21 +2569,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2593,13 +2593,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>406822</v>
+        <v>407112</v>
       </c>
       <c r="R20" t="n">
-        <v>6702171</v>
+        <v>6702395</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2665,10 +2665,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129641649</v>
+        <v>129643884</v>
       </c>
       <c r="B21" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2676,21 +2676,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2700,13 +2700,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>407112</v>
+        <v>406822</v>
       </c>
       <c r="R21" t="n">
-        <v>6702395</v>
+        <v>6702171</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 18306-2024 artfynd.xlsx
+++ b/artfynd/A 18306-2024 artfynd.xlsx
@@ -1140,10 +1140,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129645558</v>
+        <v>129641280</v>
       </c>
       <c r="B6" t="n">
-        <v>80186</v>
+        <v>79084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1151,37 +1151,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nedre värnäs, Vrm</t>
+          <t>Kolåsen, Kolåsen, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>407013</v>
+        <v>406953</v>
       </c>
       <c r="R6" t="n">
-        <v>6702313</v>
+        <v>6702246</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1208,9 +1208,19 @@
           <t>2025-11-10</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,22 +1235,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Jon Eklund</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Jon Eklund</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129641280</v>
+        <v>129645558</v>
       </c>
       <c r="B7" t="n">
-        <v>79081</v>
+        <v>80189</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1248,37 +1258,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kolåsen, Kolåsen, Vrm</t>
+          <t>Nedre värnäs, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>406953</v>
+        <v>407013</v>
       </c>
       <c r="R7" t="n">
-        <v>6702246</v>
+        <v>6702313</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1305,19 +1315,9 @@
           <t>2025-11-10</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>13:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,12 +1332,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jon Eklund</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jon Eklund</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1347,7 +1347,7 @@
         <v>129643907</v>
       </c>
       <c r="B8" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>129651079</v>
       </c>
       <c r="B9" t="n">
-        <v>91652</v>
+        <v>91655</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>129645549</v>
       </c>
       <c r="B10" t="n">
-        <v>91563</v>
+        <v>91566</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>129642118</v>
       </c>
       <c r="B11" t="n">
-        <v>97036</v>
+        <v>97040</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>129643862</v>
       </c>
       <c r="B12" t="n">
-        <v>80215</v>
+        <v>80218</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>129642502</v>
       </c>
       <c r="B13" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1966,48 +1966,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129645561</v>
+        <v>129641422</v>
       </c>
       <c r="B14" t="n">
-        <v>80146</v>
+        <v>80189</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Nedre värnäs, Vrm</t>
+          <t>Kolåsen, Kolåsen, Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>407008</v>
+        <v>407070</v>
       </c>
       <c r="R14" t="n">
-        <v>6702375</v>
+        <v>6702351</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2034,9 +2034,19 @@
           <t>2025-11-10</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2051,60 +2061,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Jon Eklund</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Jon Eklund</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129641422</v>
+        <v>129645561</v>
       </c>
       <c r="B15" t="n">
-        <v>80186</v>
+        <v>80149</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kolåsen, Kolåsen, Vrm</t>
+          <t>Nedre värnäs, Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>407070</v>
+        <v>407008</v>
       </c>
       <c r="R15" t="n">
-        <v>6702351</v>
+        <v>6702375</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2131,19 +2141,9 @@
           <t>2025-11-10</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>13:54</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2158,12 +2158,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Jon Eklund</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jon Eklund</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2173,7 +2173,7 @@
         <v>129651077</v>
       </c>
       <c r="B16" t="n">
-        <v>80215</v>
+        <v>80218</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>129651080</v>
       </c>
       <c r="B17" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>129650141</v>
       </c>
       <c r="B18" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>129645546</v>
       </c>
       <c r="B19" t="n">
-        <v>97036</v>
+        <v>97040</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         <v>129641649</v>
       </c>
       <c r="B20" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>129643884</v>
       </c>
       <c r="B21" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>129643090</v>
       </c>
       <c r="B22" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>129641549</v>
       </c>
       <c r="B23" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>129642193</v>
       </c>
       <c r="B24" t="n">
-        <v>79082</v>
+        <v>79085</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 18306-2024 artfynd.xlsx
+++ b/artfynd/A 18306-2024 artfynd.xlsx
@@ -1143,7 +1143,7 @@
         <v>129641280</v>
       </c>
       <c r="B6" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>129645558</v>
       </c>
       <c r="B7" t="n">
-        <v>80189</v>
+        <v>80192</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>129643907</v>
       </c>
       <c r="B8" t="n">
-        <v>80189</v>
+        <v>80192</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>129651079</v>
       </c>
       <c r="B9" t="n">
-        <v>91655</v>
+        <v>91658</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>129645549</v>
       </c>
       <c r="B10" t="n">
-        <v>91566</v>
+        <v>91569</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>129642118</v>
       </c>
       <c r="B11" t="n">
-        <v>97040</v>
+        <v>97043</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>129643862</v>
       </c>
       <c r="B12" t="n">
-        <v>80218</v>
+        <v>80221</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>129642502</v>
       </c>
       <c r="B13" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1966,48 +1966,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129641422</v>
+        <v>129645561</v>
       </c>
       <c r="B14" t="n">
-        <v>80189</v>
+        <v>80152</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kolåsen, Kolåsen, Vrm</t>
+          <t>Nedre värnäs, Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>407070</v>
+        <v>407008</v>
       </c>
       <c r="R14" t="n">
-        <v>6702351</v>
+        <v>6702375</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2034,19 +2034,9 @@
           <t>2025-11-10</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>13:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2061,60 +2051,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Jon Eklund</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jon Eklund</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129645561</v>
+        <v>129641422</v>
       </c>
       <c r="B15" t="n">
-        <v>80149</v>
+        <v>80192</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Nedre värnäs, Vrm</t>
+          <t>Kolåsen, Kolåsen, Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>407008</v>
+        <v>407070</v>
       </c>
       <c r="R15" t="n">
-        <v>6702375</v>
+        <v>6702351</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2141,9 +2131,19 @@
           <t>2025-11-10</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2158,44 +2158,44 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Jon Eklund</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Jon Eklund</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129651077</v>
+        <v>129651080</v>
       </c>
       <c r="B16" t="n">
-        <v>80218</v>
+        <v>80192</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2205,10 +2205,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>407042</v>
+        <v>407023</v>
       </c>
       <c r="R16" t="n">
-        <v>6702373</v>
+        <v>6702296</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2267,32 +2267,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129651080</v>
+        <v>129651077</v>
       </c>
       <c r="B17" t="n">
-        <v>80189</v>
+        <v>80221</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2302,10 +2302,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>407023</v>
+        <v>407042</v>
       </c>
       <c r="R17" t="n">
-        <v>6702296</v>
+        <v>6702373</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2367,7 +2367,7 @@
         <v>129650141</v>
       </c>
       <c r="B18" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>129645546</v>
       </c>
       <c r="B19" t="n">
-        <v>97040</v>
+        <v>97043</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         <v>129641649</v>
       </c>
       <c r="B20" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>129643884</v>
       </c>
       <c r="B21" t="n">
-        <v>80189</v>
+        <v>80192</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>129643090</v>
       </c>
       <c r="B22" t="n">
-        <v>80189</v>
+        <v>80192</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>129641549</v>
       </c>
       <c r="B23" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>129642193</v>
       </c>
       <c r="B24" t="n">
-        <v>79085</v>
+        <v>79088</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 18306-2024 artfynd.xlsx
+++ b/artfynd/A 18306-2024 artfynd.xlsx
@@ -1143,7 +1143,7 @@
         <v>129641280</v>
       </c>
       <c r="B6" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>129645558</v>
       </c>
       <c r="B7" t="n">
-        <v>80192</v>
+        <v>80193</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>129643907</v>
       </c>
       <c r="B8" t="n">
-        <v>80192</v>
+        <v>80193</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>129651079</v>
       </c>
       <c r="B9" t="n">
-        <v>91658</v>
+        <v>91659</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>129645549</v>
       </c>
       <c r="B10" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>129642118</v>
       </c>
       <c r="B11" t="n">
-        <v>97043</v>
+        <v>97044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>129643862</v>
       </c>
       <c r="B12" t="n">
-        <v>80221</v>
+        <v>80222</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>129642502</v>
       </c>
       <c r="B13" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1966,48 +1966,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129645561</v>
+        <v>129641422</v>
       </c>
       <c r="B14" t="n">
-        <v>80152</v>
+        <v>80193</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Nedre värnäs, Vrm</t>
+          <t>Kolåsen, Kolåsen, Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>407008</v>
+        <v>407070</v>
       </c>
       <c r="R14" t="n">
-        <v>6702375</v>
+        <v>6702351</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2034,9 +2034,19 @@
           <t>2025-11-10</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2051,60 +2061,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Jon Eklund</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Jon Eklund</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129641422</v>
+        <v>129645561</v>
       </c>
       <c r="B15" t="n">
-        <v>80192</v>
+        <v>80153</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kolåsen, Kolåsen, Vrm</t>
+          <t>Nedre värnäs, Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>407070</v>
+        <v>407008</v>
       </c>
       <c r="R15" t="n">
-        <v>6702351</v>
+        <v>6702375</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2131,19 +2141,9 @@
           <t>2025-11-10</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>13:54</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2158,44 +2158,44 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Jon Eklund</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jon Eklund</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129651080</v>
+        <v>129651077</v>
       </c>
       <c r="B16" t="n">
-        <v>80192</v>
+        <v>80222</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2205,10 +2205,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>407023</v>
+        <v>407042</v>
       </c>
       <c r="R16" t="n">
-        <v>6702296</v>
+        <v>6702373</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2267,32 +2267,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129651077</v>
+        <v>129651080</v>
       </c>
       <c r="B17" t="n">
-        <v>80221</v>
+        <v>80193</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2302,10 +2302,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>407042</v>
+        <v>407023</v>
       </c>
       <c r="R17" t="n">
-        <v>6702373</v>
+        <v>6702296</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2367,7 +2367,7 @@
         <v>129650141</v>
       </c>
       <c r="B18" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>129645546</v>
       </c>
       <c r="B19" t="n">
-        <v>97043</v>
+        <v>97044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2558,10 +2558,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129641649</v>
+        <v>129643884</v>
       </c>
       <c r="B20" t="n">
-        <v>79087</v>
+        <v>80193</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2569,21 +2569,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2593,13 +2593,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>407112</v>
+        <v>406822</v>
       </c>
       <c r="R20" t="n">
-        <v>6702395</v>
+        <v>6702171</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2665,10 +2665,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129643884</v>
+        <v>129641649</v>
       </c>
       <c r="B21" t="n">
-        <v>80192</v>
+        <v>79088</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2676,21 +2676,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2700,13 +2700,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>406822</v>
+        <v>407112</v>
       </c>
       <c r="R21" t="n">
-        <v>6702171</v>
+        <v>6702395</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2775,7 +2775,7 @@
         <v>129643090</v>
       </c>
       <c r="B22" t="n">
-        <v>80192</v>
+        <v>80193</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>129641549</v>
       </c>
       <c r="B23" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>129642193</v>
       </c>
       <c r="B24" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 18306-2024 artfynd.xlsx
+++ b/artfynd/A 18306-2024 artfynd.xlsx
@@ -3100,7 +3100,7 @@
         <v>120301319</v>
       </c>
       <c r="B25" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 18306-2024 artfynd.xlsx
+++ b/artfynd/A 18306-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111613147</v>
+        <v>129642118</v>
       </c>
       <c r="B2" t="n">
-        <v>89425</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,45 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kolåsen, Vrm</t>
+          <t>Kolåsen, Kolåsen, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>406870.561974647</v>
+        <v>406976</v>
       </c>
       <c r="R2" t="n">
-        <v>6702251.806638343</v>
+        <v>6702335</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,27 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-08-21</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På gammal tall med bohål.</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,34 +764,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jon Eklund</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>August Oljeqvist, Jonas Göransson</t>
+          <t>Jon Eklund</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120301256</v>
+        <v>129645546</v>
       </c>
       <c r="B3" t="n">
-        <v>78563</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,37 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>230405</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kolåsen, Vrm</t>
+          <t>Nedre värnäs, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>406846</v>
+        <v>407002</v>
       </c>
       <c r="R3" t="n">
-        <v>6702251</v>
+        <v>6702306</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,22 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:28</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:28</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,27 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jon Eklund</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jon Eklund</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120302138</v>
+        <v>129651079</v>
       </c>
       <c r="B4" t="n">
-        <v>79643</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -932,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>2079</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -956,13 +914,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>406826</v>
+        <v>407038</v>
       </c>
       <c r="R4" t="n">
-        <v>6702173</v>
+        <v>6702362</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,22 +944,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:36</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:36</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,27 +964,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sofia Damne</t>
+          <t>Ossian Tulin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sofia Damne</t>
+          <t>Ossian Tulin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120301164</v>
+        <v>111613147</v>
       </c>
       <c r="B5" t="n">
-        <v>79647</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1044,37 +987,48 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kolåsen, Kolåsen, Vrm</t>
+          <t>Kolåsen, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>406890</v>
+        <v>406870</v>
       </c>
       <c r="R5" t="n">
-        <v>6702300</v>
+        <v>6702252</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1098,22 +1052,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>11:21</t>
+          <t>2023-08-21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>11:21</t>
+          <t>2023-08-21</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På gammal tall med bohål.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,66 +1071,67 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>August Oljeqvist, Jonas Göransson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129641280</v>
+        <v>129645549</v>
       </c>
       <c r="B6" t="n">
-        <v>79088</v>
+        <v>91872</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kolåsen, Kolåsen, Vrm</t>
+          <t>Nedre värnäs, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>406953</v>
+        <v>407002</v>
       </c>
       <c r="R6" t="n">
-        <v>6702246</v>
+        <v>6702306</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1208,19 +1158,9 @@
           <t>2025-11-10</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:39</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,60 +1175,64 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jon Eklund</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jon Eklund</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129645558</v>
+        <v>120301319</v>
       </c>
       <c r="B7" t="n">
-        <v>80193</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nedre värnäs, Vrm</t>
+          <t>Kolåsen, Kolåsen, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>407013</v>
+        <v>406874</v>
       </c>
       <c r="R7" t="n">
-        <v>6702313</v>
+        <v>6702242</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1312,12 +1256,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,60 +1286,60 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Fabian Pettersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Fabian Pettersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129643907</v>
+        <v>120301635</v>
       </c>
       <c r="B8" t="n">
-        <v>80193</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kolåsen, Kolåsen, Vrm</t>
+          <t>Hällmyren, Hällmyren, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>406813</v>
+        <v>406821</v>
       </c>
       <c r="R8" t="n">
-        <v>6702148</v>
+        <v>6702285</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1409,22 +1363,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1439,60 +1393,60 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jon Eklund</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jon Eklund</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129651079</v>
+        <v>129641280</v>
       </c>
       <c r="B9" t="n">
-        <v>91659</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kolåsen, Vrm</t>
+          <t>Kolåsen, Kolåsen, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>407038</v>
+        <v>406953</v>
       </c>
       <c r="R9" t="n">
-        <v>6702362</v>
+        <v>6702246</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1519,9 +1473,19 @@
           <t>2025-11-10</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1536,60 +1500,60 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ossian Tulin</t>
+          <t>Jon Eklund</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ossian Tulin</t>
+          <t>Jon Eklund</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129645549</v>
+        <v>129641549</v>
       </c>
       <c r="B10" t="n">
-        <v>91570</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nedre värnäs, Vrm</t>
+          <t>Kolåsen, Kolåsen, Vrm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>407002</v>
+        <v>407133</v>
       </c>
       <c r="R10" t="n">
-        <v>6702306</v>
+        <v>6702349</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1616,9 +1580,19 @@
           <t>2025-11-10</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,44 +1607,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Jon Eklund</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Jon Eklund</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129642118</v>
+        <v>129641649</v>
       </c>
       <c r="B11" t="n">
-        <v>97044</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1680,13 +1654,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>406976</v>
+        <v>407112</v>
       </c>
       <c r="R11" t="n">
-        <v>6702335</v>
+        <v>6702395</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1715,7 +1689,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1725,7 +1699,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1752,32 +1726,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129643862</v>
+        <v>129642502</v>
       </c>
       <c r="B12" t="n">
-        <v>80222</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1787,10 +1761,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>406831</v>
+        <v>406915</v>
       </c>
       <c r="R12" t="n">
-        <v>6702177</v>
+        <v>6702269</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1822,7 +1796,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1832,7 +1806,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1859,14 +1833,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129642502</v>
+        <v>129650141</v>
       </c>
       <c r="B13" t="n">
-        <v>79088</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1890,17 +1864,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kolåsen, Kolåsen, Vrm</t>
+          <t>Torsby kommun, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>406915</v>
+        <v>406977</v>
       </c>
       <c r="R13" t="n">
-        <v>6702269</v>
+        <v>6702311</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1927,19 +1901,9 @@
           <t>2025-11-10</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>14:50</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1954,22 +1918,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Jon Eklund</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jon Eklund</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129641422</v>
+        <v>120301164</v>
       </c>
       <c r="B14" t="n">
-        <v>80193</v>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2001,13 +1965,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>407070</v>
+        <v>406890</v>
       </c>
       <c r="R14" t="n">
-        <v>6702351</v>
+        <v>6702300</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2031,22 +1995,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2061,60 +2025,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Jon Eklund</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jon Eklund</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129645561</v>
+        <v>120301955</v>
       </c>
       <c r="B15" t="n">
-        <v>80153</v>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Nedre värnäs, Vrm</t>
+          <t>Hällmyren, Hällmyren, Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>407008</v>
+        <v>406821</v>
       </c>
       <c r="R15" t="n">
-        <v>6702375</v>
+        <v>6702285</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2138,12 +2102,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2158,44 +2132,44 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129651077</v>
+        <v>120302138</v>
       </c>
       <c r="B16" t="n">
-        <v>80222</v>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2205,13 +2179,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>407042</v>
+        <v>406826</v>
       </c>
       <c r="R16" t="n">
-        <v>6702373</v>
+        <v>6702173</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2235,12 +2209,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2255,22 +2239,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ossian Tulin</t>
+          <t>Sofia Damne</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ossian Tulin</t>
+          <t>Sofia Damne</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129651080</v>
+        <v>120406607</v>
       </c>
       <c r="B17" t="n">
-        <v>80193</v>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2296,19 +2280,22 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kolåsen, Vrm</t>
+          <t>Lunglav, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>407023</v>
+        <v>406829</v>
       </c>
       <c r="R17" t="n">
-        <v>6702296</v>
+        <v>6702288</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2332,12 +2319,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2346,28 +2343,29 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ossian Tulin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ossian Tulin</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129650141</v>
+        <v>129641422</v>
       </c>
       <c r="B18" t="n">
-        <v>79088</v>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2375,37 +2373,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Torsby kommun, Vrm</t>
+          <t>Kolåsen, Kolåsen, Vrm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>406977</v>
+        <v>407070</v>
       </c>
       <c r="R18" t="n">
-        <v>6702311</v>
+        <v>6702351</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2432,9 +2430,19 @@
           <t>2025-11-10</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2449,22 +2457,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Jon Eklund</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Jon Eklund</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129645546</v>
+        <v>129643090</v>
       </c>
       <c r="B19" t="n">
-        <v>97044</v>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2472,37 +2480,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Nedre värnäs, Vrm</t>
+          <t>Kolåsen, Kolåsen, Vrm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>407002</v>
+        <v>406830</v>
       </c>
       <c r="R19" t="n">
-        <v>6702306</v>
+        <v>6702175</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2529,9 +2537,19 @@
           <t>2025-11-10</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2546,12 +2564,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Jon Eklund</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Jon Eklund</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2561,7 +2579,7 @@
         <v>129643884</v>
       </c>
       <c r="B20" t="n">
-        <v>80193</v>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2665,10 +2683,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129641649</v>
+        <v>129643907</v>
       </c>
       <c r="B21" t="n">
-        <v>79088</v>
+        <v>80432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2676,21 +2694,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2700,13 +2718,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>407112</v>
+        <v>406813</v>
       </c>
       <c r="R21" t="n">
-        <v>6702395</v>
+        <v>6702148</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2735,7 +2753,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2745,7 +2763,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2772,10 +2790,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129643090</v>
+        <v>129645556</v>
       </c>
       <c r="B22" t="n">
-        <v>80193</v>
+        <v>80432</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2803,17 +2821,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kolåsen, Kolåsen, Vrm</t>
+          <t>Nedre värnäs, Vrm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>406830</v>
+        <v>406982</v>
       </c>
       <c r="R22" t="n">
-        <v>6702175</v>
+        <v>6702387</v>
       </c>
       <c r="S22" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2840,19 +2858,9 @@
           <t>2025-11-10</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>14:55</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2867,22 +2875,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Jon Eklund</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jon Eklund</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129641549</v>
+        <v>129645557</v>
       </c>
       <c r="B23" t="n">
-        <v>79088</v>
+        <v>80432</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2890,37 +2898,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kolåsen, Kolåsen, Vrm</t>
+          <t>Nedre värnäs, Vrm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>407133</v>
+        <v>407007</v>
       </c>
       <c r="R23" t="n">
-        <v>6702349</v>
+        <v>6702376</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2947,19 +2955,9 @@
           <t>2025-11-10</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>14:06</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>14:06</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2974,22 +2972,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jon Eklund</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jon Eklund</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129642193</v>
+        <v>129645558</v>
       </c>
       <c r="B24" t="n">
-        <v>79089</v>
+        <v>80432</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2997,40 +2995,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>230405</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kolåsen, Kolåsen, Vrm</t>
+          <t>Nedre värnäs, Vrm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>406961</v>
+        <v>407013</v>
       </c>
       <c r="R24" t="n">
-        <v>6702296</v>
+        <v>6702313</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3057,50 +3052,39 @@
           <t>2025-11-10</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>14:43</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-11-10</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>14:43</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Jon Eklund</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Jon Eklund</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120301319</v>
+        <v>129651080</v>
       </c>
       <c r="B25" t="n">
-        <v>79246</v>
+        <v>80432</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3108,41 +3092,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kolåsen, Kolåsen, Vrm</t>
+          <t>Kolåsen, Vrm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>406874</v>
+        <v>407023</v>
       </c>
       <c r="R25" t="n">
-        <v>6702242</v>
+        <v>6702296</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3166,22 +3146,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>11:34</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>11:34</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3196,15 +3166,1029 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Fabian Pettersson</t>
+          <t>Ossian Tulin</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Fabian Pettersson</t>
+          <t>Ossian Tulin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>120302104</v>
+      </c>
+      <c r="B26" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Hällmyren, Hällmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>406821</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6702285</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129643862</v>
+      </c>
+      <c r="B27" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Kolåsen, Kolåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>406831</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6702177</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Jon Eklund</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Jon Eklund</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129651077</v>
+      </c>
+      <c r="B28" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Kolåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>407042</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6702373</v>
+      </c>
+      <c r="S28" t="n">
+        <v>15</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Ossian Tulin</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Ossian Tulin</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129645567</v>
+      </c>
+      <c r="B29" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Nedre värnäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>406983</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6702388</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129645568</v>
+      </c>
+      <c r="B30" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Nedre värnäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>407004</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6702376</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129645560</v>
+      </c>
+      <c r="B31" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Nedre värnäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>406982</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6702387</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129645561</v>
+      </c>
+      <c r="B32" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Nedre värnäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>407008</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6702375</v>
+      </c>
+      <c r="S32" t="n">
+        <v>25</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129645562</v>
+      </c>
+      <c r="B33" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Nedre värnäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>407001</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6702375</v>
+      </c>
+      <c r="S33" t="n">
+        <v>25</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>120301256</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79328</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Kolåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>406846</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6702251</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Jon Eklund</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Jon Eklund</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129642193</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79328</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Kolåsen, Kolåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>406961</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6702296</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Jon Eklund</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Jon Eklund</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18306-2024 artfynd.xlsx
+++ b/artfynd/A 18306-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AZ35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129642118</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129645546</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129651079</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1087,6 +1107,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111613147</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1184,6 +1209,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129645549</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1295,6 +1325,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120301319</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1402,6 +1437,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120301635</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1509,6 +1549,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129641280</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1616,6 +1661,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129641549</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1723,6 +1773,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129641649</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1830,6 +1885,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129642502</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1927,6 +1987,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129650141</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2034,6 +2099,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120301164</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2141,6 +2211,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120301955</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2248,6 +2323,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120302138</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2359,6 +2439,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120406607</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2466,6 +2551,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129641422</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2573,6 +2663,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129643090</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2680,6 +2775,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129643884</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2787,6 +2887,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129643907</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2884,6 +2989,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129645556</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2981,6 +3091,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129645557</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3078,6 +3193,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129645558</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3175,6 +3295,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129651080</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3282,6 +3407,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120302104</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3389,6 +3519,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129643862</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3486,6 +3621,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129651077</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3583,6 +3723,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129645567</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3680,6 +3825,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129645568</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3777,6 +3927,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129645560</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3874,6 +4029,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129645561</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3971,6 +4131,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129645562</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4078,6 +4243,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120301256</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4189,8 +4359,49 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129642193</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>